--- a/artfynd/A 49624-2025 artfynd.xlsx
+++ b/artfynd/A 49624-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>91797604</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526962.4445094545</v>
+        <v>526962</v>
       </c>
       <c r="R2" t="n">
-        <v>6986336.966379051</v>
+        <v>6986337</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,16 +791,11 @@
         <v>91797605</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526902.5302830812</v>
+        <v>526903</v>
       </c>
       <c r="R3" t="n">
-        <v>6986320.115287235</v>
+        <v>6986320</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +860,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,12 +904,7 @@
         <v>91797603</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526980.0438531009</v>
+        <v>526980</v>
       </c>
       <c r="R4" t="n">
-        <v>6986299.403406234</v>
+        <v>6986299</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,19 +973,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49624-2025 artfynd.xlsx
+++ b/artfynd/A 49624-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797604</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797605</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,8 +1026,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>